--- a/test_data_demo/demo_plancharge.xlsx
+++ b/test_data_demo/demo_plancharge.xlsx
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="138">
   <si>
     <t xml:space="preserve">05/10/26</t>
   </si>
@@ -459,7 +459,7 @@
     <t xml:space="preserve">Y99F900011</t>
   </si>
   <si>
-    <t xml:space="preserve">2GI_DEMO_1ZZZ_SiteNord_TS_TT_</t>
+    <t xml:space="preserve">2GI_DEMO_0ZZZ_SiteLoire_TS_TT_</t>
   </si>
   <si>
     <t xml:space="preserve"/>
@@ -468,7 +468,7 @@
     <t xml:space="preserve">U9FFF1</t>
   </si>
   <si>
-    <t xml:space="preserve">2GI_DEMO_1ZZZ_SiteNord_TS_TT_B</t>
+    <t xml:space="preserve">2GI_DEMO_0ZZZ_SiteLoire_TS_TT_B</t>
   </si>
   <si>
     <t xml:space="preserve">U9FFF2</t>
@@ -487,6 +487,15 @@
   </si>
   <si>
     <t xml:space="preserve">RTE</t>
+  </si>
+  <si>
+    <t>BERNARDSO</t>
+  </si>
+  <si>
+    <t>[inactif]FONTAINEE</t>
+  </si>
+  <si>
+    <t>LEROY Nathalie / Réserve de Capacité</t>
   </si>
 </sst>
 </file>
@@ -736,7 +745,7 @@
         <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>135</v>
       </c>
       <c r="C10" t="s">
         <v>35</v>
@@ -1308,7 +1317,7 @@
         <v>72</v>
       </c>
       <c r="B23" t="s">
-        <v>76</v>
+        <v>136</v>
       </c>
       <c r="C23" t="s">
         <v>77</v>
@@ -2368,10 +2377,10 @@
         <v>124</v>
       </c>
       <c r="B52" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="C52" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="D52" t="s">
         <v>25</v>
